--- a/InputData/bldgs/SYDEC/Start Year Distributed Electricity Capacity.xlsx
+++ b/InputData/bldgs/SYDEC/Start Year Distributed Electricity Capacity.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="19380" windowHeight="10380" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
@@ -39989,7 +39989,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>93.61156</v>
       </c>
     </row>
     <row r="4" ht="14.75" customHeight="1" s="49">
@@ -40031,13 +40031,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>0.15121</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>27.31469</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>175.62539</v>
       </c>
     </row>
     <row r="7" ht="14.75" customHeight="1" s="49">
@@ -40047,13 +40047,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.00134</v>
+        <v>0.9868400000000001</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.93223</v>
+        <v>178.26012</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>14.77927</v>
+        <v>454.74665</v>
       </c>
     </row>
     <row r="8" ht="14.75" customHeight="1" s="49">
@@ -40117,7 +40117,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="12" ht="14.75" customHeight="1" s="49">
